--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486330_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486330_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.7295</v>
+        <v>9.683299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.732100000000001</v>
+        <v>9.1791</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974</v>
+        <v>0.5042</v>
       </c>
       <c r="G2" t="n">
         <v>4.1621</v>
@@ -610,13 +610,13 @@
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1146</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1899</v>
+        <v>0.2572</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3045</v>
+        <v>-0.1887</v>
       </c>
       <c r="V2" t="n">
         <v>2.1901</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1061</v>
+        <v>3.0193</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7245</v>
+        <v>4.6069</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6184</v>
+        <v>-1.5876</v>
       </c>
       <c r="G3" t="n">
         <v>-1.9069</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8207</v>
+        <v>0.7339</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3193</v>
+        <v>1.2017</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4986</v>
+        <v>-0.4678</v>
       </c>
       <c r="V3" t="n">
         <v>1.7997</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3191</v>
+        <v>2.9838</v>
       </c>
       <c r="E4" t="n">
-        <v>1.762</v>
+        <v>1.4267</v>
       </c>
       <c r="F4" t="n">
         <v>1.5572</v>
@@ -766,10 +766,10 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3291</v>
+        <v>0.9938</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8051</v>
+        <v>0.4699</v>
       </c>
       <c r="U4" t="n">
         <v>0.5239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1728</v>
+        <v>1.4078</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7337</v>
+        <v>1.8455</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.4377</v>
       </c>
       <c r="G5" t="n">
         <v>1.1368</v>
@@ -844,13 +844,13 @@
         <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2038</v>
+        <v>0.0312</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3052</v>
+        <v>1.0489</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5362</v>
+        <v>3.095</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.231</v>
+        <v>-2.046</v>
       </c>
       <c r="G6" t="n">
         <v>-3.5782</v>
@@ -922,13 +922,13 @@
         <v>3.2626</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1767</v>
+        <v>-1.433</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5804</v>
+        <v>-0.0216</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5963</v>
+        <v>-1.4114</v>
       </c>
       <c r="V6" t="n">
         <v>3.8851</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>T. RICHARDSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2188</v>
+        <v>0.6787</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2404</v>
+        <v>0.3468</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0216</v>
+        <v>0.3319</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4906</v>
+        <v>-3.8163</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4078</v>
+        <v>-0.9396</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0829</v>
+        <v>-2.8767</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1121</v>
+        <v>-1.5961</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.5869</v>
+        <v>-1.1188</v>
       </c>
       <c r="L7" t="n">
-        <v>2.699</v>
+        <v>-0.4773</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.6027</v>
+        <v>-2.2202</v>
       </c>
       <c r="N7" t="n">
         <v>0.1792</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7819</v>
+        <v>-2.3994</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6101</v>
+        <v>3.4801</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.6976</v>
+        <v>3.4801</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7656</v>
+        <v>0.1499</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1093</v>
+        <v>0.6177</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6563</v>
+        <v>-0.4678</v>
       </c>
       <c r="V7" t="n">
         <v>0.8649</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. RICHARDSON</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0227</v>
+        <v>0.4345</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3238</v>
+        <v>1.2404</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3011</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8163</v>
+        <v>-1.4906</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9396</v>
+        <v>-1.4078</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8767</v>
+        <v>-0.0829</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5961</v>
+        <v>1.1121</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1188</v>
+        <v>-1.5869</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4773</v>
+        <v>2.699</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2202</v>
+        <v>-2.6027</v>
       </c>
       <c r="N8" t="n">
         <v>0.1792</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3994</v>
+        <v>-2.7819</v>
       </c>
       <c r="P8" t="n">
-        <v>3.4801</v>
+        <v>2.6101</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>3.4801</v>
+        <v>3.6976</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5515</v>
+        <v>-1.5499</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0529</v>
+        <v>-0.1093</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4986</v>
+        <v>-1.4405</v>
       </c>
       <c r="V8" t="n">
         <v>0.8649</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4149</v>
+        <v>-1.7583</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0828</v>
+        <v>-0.0468</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3321</v>
+        <v>-1.7115</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4753</v>
+        <v>0.5003</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8211000000000001</v>
+        <v>0.5505</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6542</v>
+        <v>-0.0502</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1429</v>
+        <v>1.2342</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8696</v>
+        <v>0.584</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7267</v>
+        <v>0.6502</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3324</v>
+        <v>-0.7339</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0486</v>
+        <v>-0.0335</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.381</v>
+        <v>-0.7004</v>
       </c>
       <c r="P9" t="n">
         <v>-0.435</v>
@@ -1156,28 +1156,28 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8206</v>
+        <v>-0.3031</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1476</v>
+        <v>-0.1935</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.1097</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3252</v>
+        <v>-1.5204</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3252</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7891</v>
+        <v>-1.8565</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0468</v>
+        <v>-1.208</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7423</v>
+        <v>-0.6485</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5003</v>
+        <v>-2.5564</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5505</v>
+        <v>-0.0638</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0502</v>
+        <v>-2.4926</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2342</v>
+        <v>-2.5651</v>
       </c>
       <c r="K10" t="n">
-        <v>0.584</v>
+        <v>-0.5594</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6502</v>
+        <v>-2.0057</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7339</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0335</v>
+        <v>0.4956</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7004</v>
+        <v>-0.4869</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.334</v>
+        <v>0.1328</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1935</v>
+        <v>0.2271</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1405</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5204</v>
+        <v>-0.9554</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5204</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3882</v>
+        <v>-2.6172</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4315</v>
+        <v>-0.9769</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9567</v>
+        <v>-1.6404</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5564</v>
+        <v>-1.4753</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0638</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4926</v>
+        <v>-0.6542</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5651</v>
+        <v>-0.1429</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5594</v>
+        <v>-0.8696</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0057</v>
+        <v>0.7267</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008699999999999999</v>
+        <v>-1.3324</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4956</v>
+        <v>0.0486</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4869</v>
+        <v>-1.381</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5225</v>
+        <v>-0.435</v>
       </c>
       <c r="Q11" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6183</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.3252</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.5225</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.399</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.4026</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.9554</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X11" t="n">
-        <v>-2.0854</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9874</v>
+        <v>-2.7755</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8224</v>
+        <v>-0.4871</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1651</v>
+        <v>-2.2883</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1988</v>
@@ -1390,13 +1390,13 @@
         <v>2.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.7523</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5653</v>
+        <v>-0.6886</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9995</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.2492</v>
+        <v>10.2488</v>
       </c>
       <c r="E13" t="n">
         <v>19.0216</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.772500000000001</v>
+        <v>-8.772599999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.0359</v>
+        <v>-7.035900000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8884</v>
+        <v>-2.888400000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-4.1477</v>
       </c>
       <c r="J13" t="n">
-        <v>6.834300000000001</v>
+        <v>6.8343</v>
       </c>
       <c r="K13" t="n">
         <v>-5.6843</v>
@@ -1468,16 +1468,16 @@
         <v>22.8381</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3098</v>
+        <v>-1.3099</v>
       </c>
       <c r="T13" t="n">
-        <v>2.613599999999999</v>
+        <v>2.6139</v>
       </c>
       <c r="U13" t="n">
         <v>-3.9237</v>
       </c>
       <c r="V13" t="n">
-        <v>3.3692</v>
+        <v>3.369200000000001</v>
       </c>
       <c r="W13" t="n">
         <v>17.1862</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1176</v>
+        <v>6.1023</v>
       </c>
       <c r="E14" t="n">
         <v>7.7231</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6054</v>
+        <v>-1.6208</v>
       </c>
       <c r="G14" t="n">
         <v>5.2533</v>
@@ -1546,13 +1546,13 @@
         <v>0.6525</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2792</v>
+        <v>1.2639</v>
       </c>
       <c r="T14" t="n">
         <v>0.6802</v>
       </c>
       <c r="U14" t="n">
-        <v>0.599</v>
+        <v>0.5837</v>
       </c>
       <c r="V14" t="n">
         <v>1.3252</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3262</v>
+        <v>4.0281</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2196</v>
+        <v>6.7725</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8934</v>
+        <v>-2.7444</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6451</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.584</v>
+        <v>0.286</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.4506</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3137</v>
+        <v>-0.1646</v>
       </c>
       <c r="V15" t="n">
         <v>6.7798</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8474</v>
+        <v>2.1081</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5682</v>
+        <v>1.68</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2792</v>
+        <v>0.4282</v>
       </c>
       <c r="G16" t="n">
         <v>1.1384</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>0.274</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0361</v>
+        <v>0.1478</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2379</v>
+        <v>0.3869</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5684</v>
+        <v>-0.8048</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9694</v>
+        <v>-1.1994</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5377</v>
+        <v>0.3945</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0977</v>
+        <v>1.1536</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5782</v>
+        <v>-0.0305</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5195</v>
+        <v>1.1841</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4764</v>
+        <v>0.3003</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.5411</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8559</v>
+        <v>0.8415</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3786</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9577</v>
+        <v>0.5107</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3364</v>
+        <v>0.3426</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1664</v>
+        <v>0.2367</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5924</v>
+        <v>0.6754</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5739</v>
+        <v>-0.4386</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.0647</v>
+        <v>-1.3252</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4552</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9082</v>
+        <v>-0.849</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7582</v>
+        <v>1.4164</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1501</v>
+        <v>-2.2654</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1536</v>
+        <v>2.0977</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0305</v>
+        <v>1.5782</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1841</v>
+        <v>0.5195</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3003</v>
+        <v>2.4764</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5411</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8415</v>
+        <v>1.8559</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8532999999999999</v>
+        <v>-0.3786</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5107</v>
+        <v>0.9577</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3426</v>
+        <v>-1.3364</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8667</v>
+        <v>-0.447</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1166</v>
+        <v>-0.1454</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9832</v>
+        <v>-0.3016</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>-2.0647</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PEREZ PEREZ</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4643</v>
+        <v>-3.5164</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3913</v>
+        <v>-2.2339</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0729</v>
+        <v>-1.2825</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.507</v>
+        <v>5.4387</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.09429999999999999</v>
+        <v>3.4944</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4128</v>
+        <v>1.9444</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3929</v>
+        <v>4.8053</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4655</v>
+        <v>1.6091</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0726</v>
+        <v>3.1962</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1141</v>
+        <v>0.6334</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3713</v>
+        <v>1.8853</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4854</v>
+        <v>-1.2519</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.1751</v>
+        <v>-7.8302</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-8.9178</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9127999999999999</v>
+        <v>-0.1902</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2642</v>
+        <v>0.3581</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3514</v>
+        <v>-0.5483</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.695</v>
+        <v>-0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.695</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>J. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4156</v>
+        <v>-3.9601</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6809</v>
+        <v>-3.0619</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7347</v>
+        <v>-0.8982</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4387</v>
+        <v>-0.507</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4944</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9444</v>
+        <v>-0.4128</v>
       </c>
       <c r="J20" t="n">
-        <v>4.8053</v>
+        <v>-0.3929</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6091</v>
+        <v>-1.4655</v>
       </c>
       <c r="L20" t="n">
-        <v>3.1962</v>
+        <v>1.0726</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6334</v>
+        <v>-0.1141</v>
       </c>
       <c r="N20" t="n">
-        <v>1.8853</v>
+        <v>1.3713</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2519</v>
+        <v>-1.4854</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.8302</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-8.9178</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0893</v>
+        <v>0.417</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.5936</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0004</v>
+        <v>-0.1767</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9347</v>
+        <v>-1.695</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4552</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8583</v>
+        <v>-5.1113</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2119</v>
+        <v>-0.1234</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.0703</v>
+        <v>-4.988</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0336</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2177</v>
+        <v>0.9647</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1837</v>
+        <v>0.8484</v>
       </c>
       <c r="U21" t="n">
-        <v>0.034</v>
+        <v>0.1163</v>
       </c>
       <c r="V21" t="n">
         <v>-3.3899</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3254</v>
+        <v>-6.0107</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0891</v>
+        <v>-2.2008</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.2363</v>
+        <v>-3.8099</v>
       </c>
       <c r="G22" t="n">
         <v>-4.8602</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1645</v>
+        <v>0.4792</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4266</v>
+        <v>0.3149</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2621</v>
+        <v>0.1643</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0647</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.249</v>
+        <v>-8.013800000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>8.7727</v>
+        <v>8.772599999999997</v>
       </c>
       <c r="F23" t="n">
-        <v>-19.0216</v>
+        <v>-16.7865</v>
       </c>
       <c r="G23" t="n">
         <v>7.035800000000001</v>
@@ -2248,13 +2248,13 @@
         <v>7.6125</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3098</v>
+        <v>3.5451</v>
       </c>
       <c r="T23" t="n">
-        <v>3.9238</v>
+        <v>3.9236</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6138</v>
+        <v>-0.3785999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-3.3692</v>
